--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -641,7 +641,7 @@
     <col width="38" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="34" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
@@ -662,7 +662,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.12)</t>
+          <t>End-2026 target status assessment and reporting (v0.13)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>End-2025 reporting (click the ref to see your full SR25 response)</t>
+          <t>SR25 response</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -1067,9 +1067,8 @@
     <row r="18"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="H13:K13"/>
     <mergeCell ref="B4:C8"/>
     <mergeCell ref="M6:N6"/>
     <mergeCell ref="L13:R13"/>

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -23,7 +23,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -104,18 +104,6 @@
       <sz val="11"/>
     </font>
     <font>
-      <name val="Aptos"/>
-      <b val="1"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <i val="1"/>
-      <sz val="9"/>
-    </font>
-    <font>
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="22"/>
@@ -133,8 +121,12 @@
       <sz val="11"/>
       <u val="single"/>
     </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -159,11 +151,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D9D9D9"/>
       </patternFill>
     </fill>
   </fills>
@@ -199,25 +186,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -230,7 +210,7 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -242,13 +222,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -631,7 +612,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -645,13 +626,12 @@
     <col hidden="1" width="16" customWidth="1" min="9" max="9"/>
     <col hidden="1" width="50" customWidth="1" min="10" max="10"/>
     <col hidden="1" width="24" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
-    <col width="48" customWidth="1" min="14" max="14"/>
+    <col width="30" customWidth="1" min="14" max="14"/>
     <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
-    <col width="20" customWidth="1" min="17" max="17"/>
-    <col width="24" customWidth="1" min="18" max="18"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -662,367 +642,294 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting (v0.13)</t>
+          <t>SR26 sustainability reporting (v0.14)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>End-2026 target status confirmation and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="L3" s="4" t="inlineStr">
-        <is>
-          <t>Target status assessment and definitions</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="B4" s="5" t="inlineStr">
+          <t>SR26 sustainability reporting request</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>• Confirm target status for each row below (Column L). Refer to target status definitions to the right for guidance.
-• Provide commentary on progress towards each target (Column M or N)
-• Provide supporting documentation if required (Column O), including links to images
-• Note the source of your information and any limitations (Column P), then confirm the information is accurate (Columns Q–R)
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
+• Provide supporting information if required (Column N), including links to documents or images
+• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
-• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch.
+• 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
 • Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
-      <c r="L4" s="7" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="M4" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided demonstrates that the Faculty/Portfolio has met or exceeded the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="L5" s="7" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="M5" s="8" t="inlineStr">
-        <is>
-          <t>The data and information provided indicates that the target has not been met, but there has been a significant improvement and performance is trending towards the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="L6" s="7" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="M6" s="8" t="inlineStr">
-        <is>
-          <t>Some action has been taken to address the target, but the data and information provided demonstrates that this has been insufficient to meet the target</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="L7" s="7" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="M7" s="8" t="inlineStr">
-        <is>
-          <t>No action has been taken.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="60" customHeight="1">
-      <c r="L8" s="9" t="n"/>
-    </row>
-    <row r="9">
-      <c r="L9" s="10" t="inlineStr">
-        <is>
-          <t>Note: target status definitions are under review for 2027 reporting. 2026 ratings are for internal management reporting only.</t>
-        </is>
-      </c>
-    </row>
+    </row>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8" ht="60" customHeight="1"/>
     <row r="11">
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>SaSS – Student and Scholarly Services</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="C13" s="12" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="12" t="inlineStr">
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="13" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="14" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="14" t="inlineStr">
+      <c r="D14" s="9" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E14" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr">
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="14" t="inlineStr">
+      <c r="G14" s="9" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="14" t="inlineStr">
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="14" t="inlineStr">
+      <c r="I14" s="9" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="14" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="14" t="inlineStr">
+      <c r="K14" s="9" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="15" t="inlineStr">
-        <is>
-          <t>Confirm end-2026 target status</t>
-        </is>
-      </c>
-      <c r="M14" s="15" t="inlineStr">
+      <c r="L14" s="10" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="N14" s="15" t="inlineStr">
+      <c r="M14" s="10" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="O14" s="15" t="inlineStr">
+      <c r="N14" s="10" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="P14" s="15" t="inlineStr">
+      <c r="O14" s="10" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="Q14" s="15" t="inlineStr">
+      <c r="P14" s="10" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="R14" s="15" t="inlineStr">
+      <c r="Q14" s="10" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="16" t="inlineStr"/>
-      <c r="C15" s="16" t="inlineStr"/>
-      <c r="D15" s="16" t="inlineStr"/>
-      <c r="E15" s="16" t="inlineStr"/>
-      <c r="F15" s="16" t="inlineStr"/>
-      <c r="G15" s="16" t="inlineStr"/>
-      <c r="H15" s="16" t="inlineStr"/>
-      <c r="I15" s="16" t="inlineStr"/>
-      <c r="J15" s="16" t="inlineStr"/>
-      <c r="K15" s="16" t="inlineStr"/>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>(Met or exceeded; partially met; not met; not yet started)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-A general update on activities in relation to the overarching target (Column D)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>Provide further evidence of target status assessment in the form of:
-Data and commentary in direct response to the reporting request (Column F)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>Provide any additional information to support the target status assessment (e.g. links, images, rationale for selection of target status)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
+      <c r="B15" s="11" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr"/>
+      <c r="D15" s="11" t="inlineStr"/>
+      <c r="E15" s="11" t="inlineStr"/>
+      <c r="F15" s="11" t="inlineStr"/>
+      <c r="G15" s="11" t="inlineStr"/>
+      <c r="H15" s="11" t="inlineStr"/>
+      <c r="I15" s="11" t="inlineStr"/>
+      <c r="J15" s="11" t="inlineStr"/>
+      <c r="K15" s="11" t="inlineStr"/>
+      <c r="L15" s="11" t="inlineStr">
+        <is>
+          <t>A general update on activities in relation to the overarching target (Column D)</t>
+        </is>
+      </c>
+      <c r="M15" s="11" t="inlineStr">
+        <is>
+          <t>Data and commentary in direct response to the reporting request (Column F)</t>
+        </is>
+      </c>
+      <c r="N15" s="11" t="inlineStr">
+        <is>
+          <t>Any additional information (e.g. links, images, documents)</t>
+        </is>
+      </c>
+      <c r="O15" s="11" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="Q15" s="16" t="inlineStr">
+      <c r="P15" s="11" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="R15" s="16" t="inlineStr">
+      <c r="Q15" s="11" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="18" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="18" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and co curricular learning (eg Wattle Fellowship; Melbourne Plus)</t>
         </is>
       </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 3b(vii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 3b(vii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="14" t="inlineStr">
         <is>
           <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
-      <c r="H16" s="20" t="inlineStr">
+      <c r="H16" s="15" t="inlineStr">
         <is>
           <t>3b(vii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="19" t="inlineStr">
+      <c r="I16" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="19" t="inlineStr">
+      <c r="J16" s="14" t="inlineStr">
         <is>
           <t>Number of student particpation in a sustainability activity in 2025: 466 (14% increase YTY from 2024).
 Number of total credentials released for Sustainability Advocacy in 2025: 297 (29% increase YTY from 2024)</t>
         </is>
       </c>
-      <c r="K16" s="19" t="inlineStr">
+      <c r="K16" s="14" t="inlineStr">
         <is>
           <t>See also case studies on Melbourne Plus in the Chanc. Ed. SASS spreadsheet.</t>
         </is>
       </c>
-      <c r="L16" s="21" t="n"/>
-      <c r="M16" s="21" t="n"/>
-      <c r="N16" s="21" t="n"/>
-      <c r="O16" s="21" t="n"/>
-      <c r="P16" s="21" t="n"/>
-      <c r="Q16" s="21" t="n"/>
-      <c r="R16" s="21" t="n"/>
+      <c r="L16" s="16" t="n"/>
+      <c r="M16" s="16" t="n"/>
+      <c r="N16" s="16" t="n"/>
+      <c r="O16" s="16" t="n"/>
+      <c r="P16" s="16" t="n"/>
+      <c r="Q16" s="16" t="n"/>
     </row>
     <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="12" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="13" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="18" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating how graduates contribute to sustainability through their careers or communities.</t>
         </is>
       </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 3b(ii) and rated it 'Met or exceeded' (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>In end-2025 reporting your area reported on the related SP2030 target 3b(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Can you list any notable alumni working in sustainability? (Name, course and graduating year, a short summary and a link to a profile if available; please note whether consent to be featured is likely.)
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
-      <c r="H17" s="20" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>3b(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="19" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J17" s="19" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>A sustainability approach is taken at large scale student events, including MCCs, Exams &amp; Grads (no takeaway containers, reusable cutlery and plates (partnering with Green My Plate), water refill stations etc). The previously printed graduation ceremony program was converted to a digital offering in 2025. 
 The team are reviewing the process of testamur creation to reduce waste from templates becoming superseded when updates are made to signatories. 
@@ -1051,38 +958,29 @@
 We have met our 2025 target by shifting 100% of eligible on‑campus events to food vouchers instead of catering, reducing food waste while meeting required vendor minimums."</t>
         </is>
       </c>
-      <c r="K17" s="19" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>See details in Chancellery Ed. (SASS) spreadsheet, including data on sustainability-themed event participation in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="L17" s="21" t="n"/>
-      <c r="M17" s="21" t="n"/>
-      <c r="N17" s="21" t="n"/>
-      <c r="O17" s="21" t="n"/>
-      <c r="P17" s="21" t="n"/>
-      <c r="Q17" s="21" t="n"/>
-      <c r="R17" s="21" t="n"/>
+      <c r="L17" s="16" t="n"/>
+      <c r="M17" s="16" t="n"/>
+      <c r="N17" s="16" t="n"/>
+      <c r="O17" s="16" t="n"/>
+      <c r="P17" s="16" t="n"/>
+      <c r="Q17" s="16" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
-  <mergeCells count="9">
-    <mergeCell ref="M7:N7"/>
+  <mergeCells count="4">
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="L13:R13"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="D4:G8"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="M4:N4"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation sqref="L16:L17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$B$3:$B$7</formula1>
-    </dataValidation>
-    <dataValidation sqref="Q16:Q17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
+  <dataValidations count="1">
+    <dataValidation sqref="P16:P17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
       <formula1>=Lists!$C$2:$C$4</formula1>
     </dataValidation>
   </dataValidations>
@@ -1123,7 +1021,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>End-2026 target status assessment and reporting</t>
+          <t>SR26 sustainability reporting</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1033,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
+      <c r="C5" s="18" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
@@ -1148,77 +1046,77 @@
     </row>
     <row r="6"/>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="19" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="19" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="24" t="inlineStr"/>
-      <c r="C9" s="24" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr"/>
+      <c r="C9" s="20" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="24" t="inlineStr"/>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="D9" s="20" t="inlineStr"/>
+      <c r="E9" s="20" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="24" t="inlineStr"/>
+      <c r="F9" s="20" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="21" t="n"/>
-      <c r="C10" s="21" t="n"/>
-      <c r="D10" s="21" t="n"/>
-      <c r="E10" s="21" t="n"/>
-      <c r="F10" s="21" t="n"/>
+      <c r="B10" s="16" t="n"/>
+      <c r="C10" s="16" t="n"/>
+      <c r="D10" s="16" t="n"/>
+      <c r="E10" s="16" t="n"/>
+      <c r="F10" s="16" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="21" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="21" t="n"/>
+      <c r="B11" s="16" t="n"/>
+      <c r="C11" s="16" t="n"/>
+      <c r="D11" s="16" t="n"/>
+      <c r="E11" s="16" t="n"/>
+      <c r="F11" s="16" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="21" t="n"/>
-      <c r="C12" s="21" t="n"/>
-      <c r="D12" s="21" t="n"/>
-      <c r="E12" s="21" t="n"/>
-      <c r="F12" s="21" t="n"/>
+      <c r="B12" s="16" t="n"/>
+      <c r="C12" s="16" t="n"/>
+      <c r="D12" s="16" t="n"/>
+      <c r="E12" s="16" t="n"/>
+      <c r="F12" s="16" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1269,90 +1167,90 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="25" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>Student and scholarly services</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>3b(ii)</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="14" t="inlineStr">
         <is>
           <t>The University community shows increased uptake of positive sustainability skills, knowledge and behaviours through non-formal and informal learning</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
+      <c r="D7" s="14" t="inlineStr">
         <is>
           <t>Number of sustainability-focused events and participants in 2024</t>
         </is>
       </c>
-      <c r="E7" s="19" t="inlineStr">
+      <c r="E7" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="19" t="inlineStr">
+      <c r="F7" s="14" t="inlineStr">
         <is>
           <t>A sustainability approach is taken at large scale student events, including MCCs, Exams &amp; Grads (no takeaway containers, reusable cutlery and plates (partnering with Green My Plate), water refill stations etc). The previously printed graduation ceremony program was converted to a digital offering in 2025. 
 The team are reviewing the process of testamur creation to reduce waste from templates becoming superseded when updates are made to signatories. 
@@ -1381,122 +1279,122 @@
 We have met our 2025 target by shifting 100% of eligible on‑campus events to food vouchers instead of catering, reducing food waste while meeting required vendor minimums."</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr"/>
-      <c r="H7" s="19" t="inlineStr">
+      <c r="G7" s="14" t="inlineStr"/>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>See details in Chancellery Ed. (SASS) spreadsheet, including data on sustainability-themed event participation in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>3b(vii)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>The University community shows increased uptake of positive sustainability skills, knowledge and behaviours through non-formal and informal learning</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Number of participants in Melbourne Plus sustainability stream; case studies describing participant outcomes.</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr"/>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="F8" s="14" t="inlineStr"/>
+      <c r="G8" s="14" t="inlineStr">
         <is>
           <t>Number of student particpation in a sustainability activity in 2025: 466 (14% increase YTY from 2024).
 Number of total credentials released for Sustainability Advocacy in 2025: 297 (29% increase YTY from 2024)</t>
         </is>
       </c>
-      <c r="H8" s="19" t="inlineStr">
+      <c r="H8" s="14" t="inlineStr">
         <is>
           <t>See also case studies on Melbourne Plus in the Chanc. Ed. SASS spreadsheet.</t>
         </is>
       </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="I8" s="14" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>3c</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>The University offers a suite of student-centered, formal and non-formal applied sustainability learning opportunities, informed by inter and trans-disciplinary approaches</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Number of participants in relevant applied learning, internship and volunteering opportunities</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="19" t="inlineStr"/>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr"/>
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>Number of new opportunities added to Melbourne Plus Catalogue where students can participate and earn a Sustainability Advocacy credential: 5 (bringing the total offering in the stream to 17)
 The range of these opportunities span from volunteering for campus student events contributing to sustainability, auditing campus accessibility features and infrastructures, to online learning modules.</t>
         </is>
       </c>
-      <c r="H9" s="19" t="inlineStr">
+      <c r="H9" s="14" t="inlineStr">
         <is>
           <t>See also additional data in Chanc. Ed. Spreadsheet regarding sustainability-themed events in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="I9" s="19" t="inlineStr"/>
+      <c r="I9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>4a(iv)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on.</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>List of subjects and courses with sustainability-related content</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="19" t="inlineStr">
+      <c r="F10" s="14" t="inlineStr">
         <is>
           <t>The 2026 Handbook provides an overview of sustainability-related Courses, Majors, Subjects - via the Search function. 
 This builds on the 2017-2020 Sustainabilty Plan which requires Faculties to incorporate sustainability knowledge and values into the Graduate Attributes of courses.</t>
         </is>
       </c>
-      <c r="G10" s="19" t="inlineStr"/>
-      <c r="H10" s="19" t="inlineStr"/>
-      <c r="I10" s="19" t="inlineStr"/>
+      <c r="G10" s="14" t="inlineStr"/>
+      <c r="H10" s="14" t="inlineStr"/>
+      <c r="I10" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1554,309 +1452,309 @@
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="22" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="12" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="13" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="14" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="14" t="inlineStr">
+      <c r="G6" s="9" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="14" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="14" t="inlineStr">
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="15" t="inlineStr">
+      <c r="K6" s="10" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="15" t="inlineStr">
+      <c r="L6" s="10" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="15" t="inlineStr">
+      <c r="M6" s="10" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="15" t="inlineStr">
+      <c r="N6" s="10" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="15" t="inlineStr">
+      <c r="O6" s="10" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="27" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr"/>
-      <c r="D7" s="27" t="inlineStr"/>
-      <c r="E7" s="27" t="inlineStr"/>
-      <c r="F7" s="27" t="inlineStr"/>
-      <c r="G7" s="27" t="inlineStr"/>
-      <c r="H7" s="27" t="inlineStr"/>
-      <c r="I7" s="27" t="inlineStr"/>
-      <c r="J7" s="27" t="inlineStr"/>
-      <c r="K7" s="27" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr"/>
+      <c r="D7" s="23" t="inlineStr"/>
+      <c r="E7" s="23" t="inlineStr"/>
+      <c r="F7" s="23" t="inlineStr"/>
+      <c r="G7" s="23" t="inlineStr"/>
+      <c r="H7" s="23" t="inlineStr"/>
+      <c r="I7" s="23" t="inlineStr"/>
+      <c r="J7" s="23" t="inlineStr"/>
+      <c r="K7" s="23" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="27" t="inlineStr">
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="27" t="inlineStr">
+      <c r="M7" s="23" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="27" t="inlineStr">
+      <c r="N7" s="23" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="27" t="inlineStr">
+      <c r="O7" s="23" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and cocurricular learning</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>Number of Co-curricular Learning</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F8" s="28" t="n"/>
-      <c r="G8" s="28" t="n">
+      <c r="F8" s="24" t="n"/>
+      <c r="G8" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="24" t="n">
         <v>22</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="24" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="19" t="inlineStr">
+      <c r="J8" s="14" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
+      <c r="K8" s="16" t="n"/>
+      <c r="L8" s="16" t="n"/>
+      <c r="M8" s="16" t="n"/>
+      <c r="N8" s="16" t="n"/>
+      <c r="O8" s="16" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr"/>
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>Number of Experiential Learning Projects</t>
         </is>
       </c>
-      <c r="E9" s="19" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F9" s="28" t="n"/>
-      <c r="G9" s="28" t="n"/>
-      <c r="H9" s="28" t="n"/>
-      <c r="I9" s="28" t="n"/>
-      <c r="J9" s="19" t="inlineStr">
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="24" t="n"/>
+      <c r="H9" s="24" t="n"/>
+      <c r="I9" s="24" t="n"/>
+      <c r="J9" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="19" t="n"/>
-      <c r="L9" s="19" t="n"/>
-      <c r="M9" s="19" t="n"/>
-      <c r="N9" s="19" t="n"/>
-      <c r="O9" s="19" t="n"/>
+      <c r="K9" s="14" t="n"/>
+      <c r="L9" s="14" t="n"/>
+      <c r="M9" s="14" t="n"/>
+      <c r="N9" s="14" t="n"/>
+      <c r="O9" s="14" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="inlineStr">
         <is>
           <t>Number of Participating Students</t>
         </is>
       </c>
-      <c r="E10" s="19" t="inlineStr">
+      <c r="E10" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F10" s="28" t="n"/>
-      <c r="G10" s="28" t="n"/>
-      <c r="H10" s="28" t="n"/>
-      <c r="I10" s="28" t="n"/>
-      <c r="J10" s="19" t="inlineStr">
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="24" t="n"/>
+      <c r="H10" s="24" t="n"/>
+      <c r="I10" s="24" t="n"/>
+      <c r="J10" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="19" t="n"/>
-      <c r="L10" s="19" t="n"/>
-      <c r="M10" s="19" t="n"/>
-      <c r="N10" s="19" t="n"/>
-      <c r="O10" s="19" t="n"/>
+      <c r="K10" s="14" t="n"/>
+      <c r="L10" s="14" t="n"/>
+      <c r="M10" s="14" t="n"/>
+      <c r="N10" s="14" t="n"/>
+      <c r="O10" s="14" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating how graduates contribute to sustainability through their careers or communities</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
         <is>
           <t>Alumni that contribute to sustainability</t>
         </is>
       </c>
-      <c r="E11" s="19" t="inlineStr">
+      <c r="E11" s="14" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F11" s="28" t="n"/>
-      <c r="G11" s="28" t="n"/>
-      <c r="H11" s="28" t="n"/>
-      <c r="I11" s="28" t="n"/>
-      <c r="J11" s="19" t="inlineStr">
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="24" t="n"/>
+      <c r="H11" s="24" t="n"/>
+      <c r="I11" s="24" t="n"/>
+      <c r="J11" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="21" t="n"/>
-      <c r="L11" s="21" t="n"/>
-      <c r="M11" s="21" t="n"/>
-      <c r="N11" s="21" t="n"/>
-      <c r="O11" s="21" t="n"/>
+      <c r="K11" s="16" t="n"/>
+      <c r="L11" s="16" t="n"/>
+      <c r="M11" s="16" t="n"/>
+      <c r="N11" s="16" t="n"/>
+      <c r="O11" s="16" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr"/>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating sustainability contribution</t>
         </is>
       </c>
-      <c r="E12" s="19" t="inlineStr">
+      <c r="E12" s="14" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F12" s="28" t="n"/>
-      <c r="G12" s="28" t="n"/>
-      <c r="H12" s="28" t="n"/>
-      <c r="I12" s="28" t="n"/>
-      <c r="J12" s="19" t="inlineStr">
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="24" t="n"/>
+      <c r="H12" s="24" t="n"/>
+      <c r="I12" s="24" t="n"/>
+      <c r="J12" s="14" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="19" t="n"/>
-      <c r="L12" s="19" t="n"/>
-      <c r="M12" s="19" t="n"/>
-      <c r="N12" s="19" t="n"/>
-      <c r="O12" s="19" t="n"/>
+      <c r="K12" s="14" t="n"/>
+      <c r="L12" s="14" t="n"/>
+      <c r="M12" s="14" t="n"/>
+      <c r="N12" s="14" t="n"/>
+      <c r="O12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1880,13 +1778,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:I9"/>
+  <dimension ref="B1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" t="inlineStr">
         <is>
-          <t>End 2026 target status</t>
+          <t>(not used – no target status rating in 2026)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -1902,21 +1800,6 @@
       <c r="E1" t="inlineStr">
         <is>
           <t>Y/N</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Target status</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Score</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Response count</t>
         </is>
       </c>
     </row>
@@ -1941,24 +1824,8 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>3</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Met or exceeded</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1974,24 +1841,8 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
-      <c r="I3" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Partially met</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -2007,47 +1858,15 @@
           <t>TBC</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Not met</t>
-        </is>
-      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Not yet started</t>
-        </is>
-      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
@@ -2055,11 +1874,6 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Not applicable</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.14)</t>
+          <t>SR26 sustainability reporting (v0.15)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -642,7 +642,7 @@
       </c>
       <c r="B1" s="2" t="inlineStr">
         <is>
-          <t>SR26 sustainability reporting (v0.15)</t>
+          <t>SR26 sustainability reporting (v0.16)</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -23,21 +23,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.##"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Aptos"/>
-      <color rgb="00002060"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos"/>
@@ -186,65 +178,63 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -634,32 +624,22 @@
     <col width="24" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting (v0.16)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -675,261 +655,264 @@
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="60" customHeight="1"/>
-    <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11" ht="39" customHeight="1">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>SaSS – Student and Scholarly Services</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="C13" s="7" t="inlineStr">
+    <row r="12"/>
+    <row r="13" ht="27" customHeight="1">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="8" t="inlineStr">
+      <c r="L13" s="6" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="9" t="inlineStr">
+    <row r="14" ht="60" customHeight="1">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="9" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="9" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="9" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="9" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="9" t="inlineStr">
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="9" t="inlineStr">
+      <c r="K14" s="7" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="10" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="10" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="10" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="10" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="10" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="10" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="B15" s="11" t="inlineStr"/>
-      <c r="C15" s="11" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr"/>
-      <c r="E15" s="11" t="inlineStr"/>
-      <c r="F15" s="11" t="inlineStr"/>
-      <c r="G15" s="11" t="inlineStr"/>
-      <c r="H15" s="11" t="inlineStr"/>
-      <c r="I15" s="11" t="inlineStr"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="11" t="inlineStr"/>
-      <c r="L15" s="11" t="inlineStr">
+    <row r="15" ht="81" customHeight="1">
+      <c r="B15" s="9" t="inlineStr"/>
+      <c r="C15" s="9" t="inlineStr"/>
+      <c r="D15" s="9" t="inlineStr"/>
+      <c r="E15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
+      <c r="I15" s="9" t="inlineStr"/>
+      <c r="J15" s="9" t="inlineStr"/>
+      <c r="K15" s="9" t="inlineStr"/>
+      <c r="L15" s="9" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="11" t="inlineStr">
+      <c r="M15" s="9" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="11" t="inlineStr">
+      <c r="N15" s="9" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="11" t="inlineStr">
+      <c r="O15" s="9" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="11" t="inlineStr">
+      <c r="P15" s="9" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="11" t="inlineStr">
+      <c r="Q15" s="9" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="150" customHeight="1">
-      <c r="B16" s="12" t="inlineStr">
+    <row r="16" ht="254" customHeight="1">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="13" t="inlineStr">
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and co curricular learning (eg Wattle Fellowship; Melbourne Plus)</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 3b(vii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G16" s="14" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
-      <c r="H16" s="15" t="inlineStr">
+      <c r="H16" s="13" t="inlineStr">
         <is>
           <t>3b(vii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="14" t="inlineStr">
+      <c r="I16" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="14" t="inlineStr">
+      <c r="J16" s="12" t="inlineStr">
         <is>
           <t>Number of student particpation in a sustainability activity in 2025: 466 (14% increase YTY from 2024).
 Number of total credentials released for Sustainability Advocacy in 2025: 297 (29% increase YTY from 2024)</t>
         </is>
       </c>
-      <c r="K16" s="14" t="inlineStr">
+      <c r="K16" s="12" t="inlineStr">
         <is>
           <t>See also case studies on Melbourne Plus in the Chanc. Ed. SASS spreadsheet.</t>
         </is>
       </c>
-      <c r="L16" s="16" t="n"/>
-      <c r="M16" s="16" t="n"/>
-      <c r="N16" s="16" t="n"/>
-      <c r="O16" s="16" t="n"/>
-      <c r="P16" s="16" t="n"/>
-      <c r="Q16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="150" customHeight="1">
-      <c r="B17" s="12" t="inlineStr">
+      <c r="L16" s="14" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
+      <c r="P16" s="14" t="n"/>
+      <c r="Q16" s="14" t="n"/>
+    </row>
+    <row r="17" ht="220" customHeight="1">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="11" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="13" t="inlineStr">
+      <c r="E17" s="11" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating how graduates contribute to sustainability through their careers or communities.</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="12" t="inlineStr">
         <is>
           <t>In end-2025 reporting your area reported on the related SP2030 target 3b(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
 Can you list any notable alumni working in sustainability? (Name, course and graduating year, a short summary and a link to a profile if available; please note whether consent to be featured is likely.)
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="12" t="inlineStr">
         <is>
           <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
-      <c r="H17" s="15" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>3b(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="12" t="inlineStr">
         <is>
           <t>A sustainability approach is taken at large scale student events, including MCCs, Exams &amp; Grads (no takeaway containers, reusable cutlery and plates (partnering with Green My Plate), water refill stations etc). The previously printed graduation ceremony program was converted to a digital offering in 2025. 
 The team are reviewing the process of testamur creation to reduce waste from templates becoming superseded when updates are made to signatories. 
@@ -958,17 +941,17 @@
 We have met our 2025 target by shifting 100% of eligible on‑campus events to food vouchers instead of catering, reducing food waste while meeting required vendor minimums."</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K17" s="12" t="inlineStr">
         <is>
           <t>See details in Chancellery Ed. (SASS) spreadsheet, including data on sustainability-themed event participation in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="L17" s="16" t="n"/>
-      <c r="M17" s="16" t="n"/>
-      <c r="N17" s="16" t="n"/>
-      <c r="O17" s="16" t="n"/>
-      <c r="P17" s="16" t="n"/>
-      <c r="Q17" s="16" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
+      <c r="N17" s="14" t="n"/>
+      <c r="O17" s="14" t="n"/>
+      <c r="P17" s="14" t="n"/>
+      <c r="Q17" s="14" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
@@ -1013,110 +996,102 @@
     <col width="30" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>SR26 sustainability reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="17" t="inlineStr">
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
-    <row r="8">
-      <c r="B8" s="19" t="inlineStr">
+    <row r="7"/>
+    <row r="8" ht="39" customHeight="1">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="19" t="inlineStr">
+      <c r="E8" s="17" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="19" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="20" t="inlineStr"/>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr"/>
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr"/>
-      <c r="E9" s="20" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr"/>
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr"/>
+      <c r="F9" s="18" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="16" t="n"/>
-      <c r="C10" s="16" t="n"/>
-      <c r="D10" s="16" t="n"/>
-      <c r="E10" s="16" t="n"/>
-      <c r="F10" s="16" t="n"/>
+      <c r="B10" s="14" t="n"/>
+      <c r="C10" s="14" t="n"/>
+      <c r="D10" s="14" t="n"/>
+      <c r="E10" s="14" t="n"/>
+      <c r="F10" s="14" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="16" t="n"/>
-      <c r="C11" s="16" t="n"/>
-      <c r="D11" s="16" t="n"/>
-      <c r="E11" s="16" t="n"/>
-      <c r="F11" s="16" t="n"/>
+      <c r="B11" s="14" t="n"/>
+      <c r="C11" s="14" t="n"/>
+      <c r="D11" s="14" t="n"/>
+      <c r="E11" s="14" t="n"/>
+      <c r="F11" s="14" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n"/>
-      <c r="D12" s="16" t="n"/>
-      <c r="E12" s="16" t="n"/>
-      <c r="F12" s="16" t="n"/>
+      <c r="B12" s="14" t="n"/>
+      <c r="C12" s="14" t="n"/>
+      <c r="D12" s="14" t="n"/>
+      <c r="E12" s="14" t="n"/>
+      <c r="F12" s="14" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1147,110 +1122,99 @@
     <col width="16" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2025 target status assessment and reporting (for reference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Your SR25 responses – Student and Scholarly Services (SaSS)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="B4" s="21" t="inlineStr">
+    <row r="4" ht="22" customHeight="1">
+      <c r="B4" s="19" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="22" t="inlineStr">
+    <row r="5" ht="30" customHeight="1">
+      <c r="B5" s="20" t="inlineStr">
         <is>
           <t>Student and scholarly services</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="42" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="160" customHeight="1">
-      <c r="B7" s="12" t="inlineStr">
+    <row r="7" ht="409" customHeight="1">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>3b(ii)</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>The University community shows increased uptake of positive sustainability skills, knowledge and behaviours through non-formal and informal learning</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>Number of sustainability-focused events and participants in 2024</t>
         </is>
       </c>
-      <c r="E7" s="14" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr">
+      <c r="F7" s="12" t="inlineStr">
         <is>
           <t>A sustainability approach is taken at large scale student events, including MCCs, Exams &amp; Grads (no takeaway containers, reusable cutlery and plates (partnering with Green My Plate), water refill stations etc). The previously printed graduation ceremony program was converted to a digital offering in 2025. 
 The team are reviewing the process of testamur creation to reduce waste from templates becoming superseded when updates are made to signatories. 
@@ -1279,122 +1243,122 @@
 We have met our 2025 target by shifting 100% of eligible on‑campus events to food vouchers instead of catering, reducing food waste while meeting required vendor minimums."</t>
         </is>
       </c>
-      <c r="G7" s="14" t="inlineStr"/>
-      <c r="H7" s="14" t="inlineStr">
+      <c r="G7" s="12" t="inlineStr"/>
+      <c r="H7" s="12" t="inlineStr">
         <is>
           <t>See details in Chancellery Ed. (SASS) spreadsheet, including data on sustainability-themed event participation in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="I7" s="12" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>3b(vii)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>The University community shows increased uptake of positive sustainability skills, knowledge and behaviours through non-formal and informal learning</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Number of participants in Melbourne Plus sustainability stream; case studies describing participant outcomes.</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="14" t="inlineStr">
+      <c r="F8" s="12" t="inlineStr"/>
+      <c r="G8" s="12" t="inlineStr">
         <is>
           <t>Number of student particpation in a sustainability activity in 2025: 466 (14% increase YTY from 2024).
 Number of total credentials released for Sustainability Advocacy in 2025: 297 (29% increase YTY from 2024)</t>
         </is>
       </c>
-      <c r="H8" s="14" t="inlineStr">
+      <c r="H8" s="12" t="inlineStr">
         <is>
           <t>See also case studies on Melbourne Plus in the Chanc. Ed. SASS spreadsheet.</t>
         </is>
       </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="I8" s="12" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>3c</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>The University offers a suite of student-centered, formal and non-formal applied sustainability learning opportunities, informed by inter and trans-disciplinary approaches</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Number of participants in relevant applied learning, internship and volunteering opportunities</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr"/>
-      <c r="G9" s="14" t="inlineStr">
+      <c r="F9" s="12" t="inlineStr"/>
+      <c r="G9" s="12" t="inlineStr">
         <is>
           <t>Number of new opportunities added to Melbourne Plus Catalogue where students can participate and earn a Sustainability Advocacy credential: 5 (bringing the total offering in the stream to 17)
 The range of these opportunities span from volunteering for campus student events contributing to sustainability, auditing campus accessibility features and infrastructures, to online learning modules.</t>
         </is>
       </c>
-      <c r="H9" s="14" t="inlineStr">
+      <c r="H9" s="12" t="inlineStr">
         <is>
           <t>See also additional data in Chanc. Ed. Spreadsheet regarding sustainability-themed events in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="I9" s="14" t="inlineStr"/>
+      <c r="I9" s="12" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>4a(iv)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on.</t>
         </is>
       </c>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>List of subjects and courses with sustainability-related content</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr">
+      <c r="F10" s="12" t="inlineStr">
         <is>
           <t>The 2026 Handbook provides an overview of sustainability-related Courses, Majors, Subjects - via the Search function. 
 This builds on the 2017-2020 Sustainabilty Plan which requires Faculties to incorporate sustainability knowledge and values into the Graduate Attributes of courses.</t>
         </is>
       </c>
-      <c r="G10" s="14" t="inlineStr"/>
-      <c r="H10" s="14" t="inlineStr"/>
-      <c r="I10" s="14" t="inlineStr"/>
+      <c r="G10" s="12" t="inlineStr"/>
+      <c r="H10" s="12" t="inlineStr"/>
+      <c r="I10" s="12" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1416,6 +1380,7 @@
   <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
@@ -1432,329 +1397,319 @@
     <col width="26" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>End-2026 target status assessment and reporting</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="3" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="39" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
         <is>
           <t>Quantitative data – Student and Scholarly Services (SaSS)</t>
         </is>
       </c>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="B5" s="7" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="27" customHeight="1">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="K5" s="6" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="B6" s="9" t="inlineStr">
+    <row r="6" ht="60" customHeight="1">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="9" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="9" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="9" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="9" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="9" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="10" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="10" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="10" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="10" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="10" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+    <row r="7" ht="46" customHeight="1">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr"/>
-      <c r="D7" s="23" t="inlineStr"/>
-      <c r="E7" s="23" t="inlineStr"/>
-      <c r="F7" s="23" t="inlineStr"/>
-      <c r="G7" s="23" t="inlineStr"/>
-      <c r="H7" s="23" t="inlineStr"/>
-      <c r="I7" s="23" t="inlineStr"/>
-      <c r="J7" s="23" t="inlineStr"/>
-      <c r="K7" s="23" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="21" t="inlineStr"/>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+      <c r="I7" s="21" t="inlineStr"/>
+      <c r="J7" s="21" t="inlineStr"/>
+      <c r="K7" s="21" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="23" t="inlineStr">
+      <c r="M7" s="21" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="23" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="12" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and cocurricular learning</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>Number of Co-curricular Learning</t>
         </is>
       </c>
-      <c r="E8" s="14" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F8" s="24" t="n"/>
-      <c r="G8" s="24" t="n">
+      <c r="F8" s="22" t="n"/>
+      <c r="G8" s="22" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="24" t="n">
+      <c r="H8" s="22" t="n">
         <v>22</v>
       </c>
-      <c r="I8" s="24" t="n">
+      <c r="I8" s="22" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="14" t="inlineStr">
+      <c r="J8" s="12" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K8" s="16" t="n"/>
-      <c r="L8" s="16" t="n"/>
-      <c r="M8" s="16" t="n"/>
-      <c r="N8" s="16" t="n"/>
-      <c r="O8" s="16" t="n"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="12" t="inlineStr">
+      <c r="K8" s="14" t="n"/>
+      <c r="L8" s="14" t="n"/>
+      <c r="M8" s="14" t="n"/>
+      <c r="N8" s="14" t="n"/>
+      <c r="O8" s="14" t="n"/>
+    </row>
+    <row r="9" ht="39" customHeight="1">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr"/>
-      <c r="D9" s="14" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr"/>
+      <c r="D9" s="12" t="inlineStr">
         <is>
           <t>Number of Experiential Learning Projects</t>
         </is>
       </c>
-      <c r="E9" s="14" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F9" s="24" t="n"/>
-      <c r="G9" s="24" t="n"/>
-      <c r="H9" s="24" t="n"/>
-      <c r="I9" s="24" t="n"/>
-      <c r="J9" s="14" t="inlineStr">
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="14" t="n"/>
-      <c r="L9" s="14" t="n"/>
-      <c r="M9" s="14" t="n"/>
-      <c r="N9" s="14" t="n"/>
-      <c r="O9" s="14" t="n"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="12" t="inlineStr">
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
+    </row>
+    <row r="10" ht="39" customHeight="1">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C10" s="14" t="inlineStr"/>
-      <c r="D10" s="14" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr"/>
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Number of Participating Students</t>
         </is>
       </c>
-      <c r="E10" s="14" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F10" s="24" t="n"/>
-      <c r="G10" s="24" t="n"/>
-      <c r="H10" s="24" t="n"/>
-      <c r="I10" s="24" t="n"/>
-      <c r="J10" s="14" t="inlineStr">
+      <c r="F10" s="22" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="14" t="n"/>
-      <c r="L10" s="14" t="n"/>
-      <c r="M10" s="14" t="n"/>
-      <c r="N10" s="14" t="n"/>
-      <c r="O10" s="14" t="n"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="12" t="inlineStr">
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
+    </row>
+    <row r="11" ht="72" customHeight="1">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating how graduates contribute to sustainability through their careers or communities</t>
         </is>
       </c>
-      <c r="D11" s="14" t="inlineStr">
+      <c r="D11" s="12" t="inlineStr">
         <is>
           <t>Alumni that contribute to sustainability</t>
         </is>
       </c>
-      <c r="E11" s="14" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F11" s="24" t="n"/>
-      <c r="G11" s="24" t="n"/>
-      <c r="H11" s="24" t="n"/>
-      <c r="I11" s="24" t="n"/>
-      <c r="J11" s="14" t="inlineStr">
+      <c r="F11" s="22" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="16" t="n"/>
-      <c r="L11" s="16" t="n"/>
-      <c r="M11" s="16" t="n"/>
-      <c r="N11" s="16" t="n"/>
-      <c r="O11" s="16" t="n"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="12" t="inlineStr">
+      <c r="K11" s="14" t="n"/>
+      <c r="L11" s="14" t="n"/>
+      <c r="M11" s="14" t="n"/>
+      <c r="N11" s="14" t="n"/>
+      <c r="O11" s="14" t="n"/>
+    </row>
+    <row r="12" ht="39" customHeight="1">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C12" s="14" t="inlineStr"/>
-      <c r="D12" s="14" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating sustainability contribution</t>
         </is>
       </c>
-      <c r="E12" s="14" t="inlineStr">
+      <c r="E12" s="12" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F12" s="24" t="n"/>
-      <c r="G12" s="24" t="n"/>
-      <c r="H12" s="24" t="n"/>
-      <c r="I12" s="24" t="n"/>
-      <c r="J12" s="14" t="inlineStr">
+      <c r="F12" s="22" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="12" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="14" t="n"/>
-      <c r="L12" s="14" t="n"/>
-      <c r="M12" s="14" t="n"/>
-      <c r="N12" s="14" t="n"/>
-      <c r="O12" s="14" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1778,10 +1733,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:E9"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="B1" t="inlineStr">
         <is>
           <t>(not used – no target status rating in 2026)</t>
@@ -1803,7 +1765,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
+    <row r="2" ht="22" customHeight="1">
       <c r="B2" t="inlineStr">
         <is>
           <t>Please select from dropdown</t>
@@ -1825,7 +1787,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
+    <row r="3" ht="22" customHeight="1">
       <c r="C3" t="inlineStr">
         <is>
           <t>No</t>
@@ -1842,7 +1804,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
+    <row r="4" ht="22" customHeight="1">
       <c r="C4" t="inlineStr">
         <is>
           <t>Partially – see comments</t>
@@ -1859,35 +1821,35 @@
         </is>
       </c>
     </row>
-    <row r="5">
+    <row r="5" ht="22" customHeight="1">
       <c r="D5" t="inlineStr">
         <is>
           <t>Received</t>
         </is>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="22" customHeight="1">
       <c r="D6" t="inlineStr">
         <is>
           <t>First review</t>
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="22" customHeight="1">
       <c r="D7" t="inlineStr">
         <is>
           <t>Follow-up</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="22" customHeight="1">
       <c r="D8" t="inlineStr">
         <is>
           <t>Complete</t>
         </is>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="22" customHeight="1">
       <c r="D9" t="inlineStr">
         <is>
           <t>Not required</t>

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -647,7 +647,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: CDSS – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -34,7 +34,7 @@
     <font>
       <name val="Aptos"/>
       <b val="1"/>
-      <color rgb="00002060"/>
+      <color rgb="00FFFFFF"/>
       <sz val="22"/>
     </font>
     <font>
@@ -118,7 +118,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -143,6 +143,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C1E4F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00000F46"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,9 +183,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="4"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -311,6 +319,126 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>57150</colOff>
+      <row>1</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <ext cx="609600" cy="609600"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -602,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -622,24 +750,61 @@
     <col width="30" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>SR26 sustainability reporting request</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4">
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>How to use this spreadsheet:</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
@@ -647,7 +812,7 @@
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
-• Due: Tuesday 15 December 2026. Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
+• Due: Thursday 24 December 2026 (Christmas shutdown). Questions: Sustainability Strategy team (SST) – questions and clarifications are recorded centrally (contact email TBC); optional 1:1 meetings available on request</t>
         </is>
       </c>
     </row>
@@ -658,7 +823,7 @@
     <row r="9"/>
     <row r="10"/>
     <row r="11" ht="39" customHeight="1">
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>SaSS – Student and Scholarly Services</t>
         </is>
@@ -666,253 +831,253 @@
     </row>
     <row r="12"/>
     <row r="13" ht="27" customHeight="1">
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>Sustainability 2030 target and indicator</t>
         </is>
       </c>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="6" t="inlineStr">
         <is>
           <t>SR25 response</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="7" t="inlineStr">
         <is>
           <t>End-2026 reporting (PLEASE COMPLETE THIS SECTION)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="60" customHeight="1">
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>Priority area</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
+      <c r="D14" s="8" t="inlineStr">
         <is>
           <t>Sustainability 2030 target</t>
         </is>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
+      <c r="F14" s="8" t="inlineStr">
         <is>
           <t>2026 Reporting request</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>How SST will use this data</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="H14" s="8" t="inlineStr">
         <is>
           <t>Related SR25 ref</t>
         </is>
       </c>
-      <c r="I14" s="7" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>End-2025 confirmed status</t>
         </is>
       </c>
-      <c r="J14" s="7" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>End-2025 reporting response</t>
         </is>
       </c>
-      <c r="K14" s="7" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t>Links and supporting information</t>
         </is>
       </c>
-      <c r="L14" s="8" t="inlineStr">
+      <c r="L14" s="9" t="inlineStr">
         <is>
           <t>OPTION 1:  Target-level reporting (Column D)</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="M14" s="9" t="inlineStr">
         <is>
           <t>OPTION 2:  Indicator level reporting (Column E/F)</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="N14" s="9" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="O14" s="9" t="inlineStr">
         <is>
           <t>Data source and limitations</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="P14" s="9" t="inlineStr">
         <is>
           <t>Data owner confirms information is accurate</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="Q14" s="9" t="inlineStr">
         <is>
           <t>Confirmed by (name, role, date)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="81" customHeight="1">
-      <c r="B15" s="9" t="inlineStr"/>
-      <c r="C15" s="9" t="inlineStr"/>
-      <c r="D15" s="9" t="inlineStr"/>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
-      <c r="G15" s="9" t="inlineStr"/>
-      <c r="H15" s="9" t="inlineStr"/>
-      <c r="I15" s="9" t="inlineStr"/>
-      <c r="J15" s="9" t="inlineStr"/>
-      <c r="K15" s="9" t="inlineStr"/>
-      <c r="L15" s="9" t="inlineStr">
+      <c r="B15" s="10" t="inlineStr"/>
+      <c r="C15" s="10" t="inlineStr"/>
+      <c r="D15" s="10" t="inlineStr"/>
+      <c r="E15" s="10" t="inlineStr"/>
+      <c r="F15" s="10" t="inlineStr"/>
+      <c r="G15" s="10" t="inlineStr"/>
+      <c r="H15" s="10" t="inlineStr"/>
+      <c r="I15" s="10" t="inlineStr"/>
+      <c r="J15" s="10" t="inlineStr"/>
+      <c r="K15" s="10" t="inlineStr"/>
+      <c r="L15" s="10" t="inlineStr">
         <is>
           <t>A general update on activities in relation to the overarching target (Column D)</t>
         </is>
       </c>
-      <c r="M15" s="9" t="inlineStr">
+      <c r="M15" s="10" t="inlineStr">
         <is>
           <t>Data and commentary in direct response to the reporting request (Column F)</t>
         </is>
       </c>
-      <c r="N15" s="9" t="inlineStr">
+      <c r="N15" s="10" t="inlineStr">
         <is>
           <t>Any additional information (e.g. links, images, documents)</t>
         </is>
       </c>
-      <c r="O15" s="9" t="inlineStr">
+      <c r="O15" s="10" t="inlineStr">
         <is>
           <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
         </is>
       </c>
-      <c r="P15" s="9" t="inlineStr">
+      <c r="P15" s="10" t="inlineStr">
         <is>
           <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
         </is>
       </c>
-      <c r="Q15" s="9" t="inlineStr">
+      <c r="Q15" s="10" t="inlineStr">
         <is>
           <t>Name, role and date of the person confirming</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="254" customHeight="1">
-      <c r="B16" s="10" t="inlineStr">
+    <row r="16" ht="220" customHeight="1">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C16" s="11" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E16" s="11" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and co curricular learning (eg Wattle Fellowship; Melbourne Plus)</t>
         </is>
       </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 3b(vii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.
+      <c r="F16" s="13" t="inlineStr">
+        <is>
+          <t>Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.
+In end-2025 reporting your area reported on the related SP2030 target 3b(vii) (click the ref in Column H to see it in full in Tab 3).
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="G16" s="13" t="inlineStr">
         <is>
           <t>We will combine faculty examples with central Wattle Fellowship and Melbourne Plus data to report on the range and reach of sustainability-focused experiential and co-curricular learning across the University.</t>
         </is>
       </c>
-      <c r="H16" s="13" t="inlineStr">
+      <c r="H16" s="14" t="inlineStr">
         <is>
           <t>3b(vii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I16" s="12" t="inlineStr">
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J16" s="12" t="inlineStr">
+      <c r="J16" s="13" t="inlineStr">
         <is>
           <t>Number of student particpation in a sustainability activity in 2025: 466 (14% increase YTY from 2024).
 Number of total credentials released for Sustainability Advocacy in 2025: 297 (29% increase YTY from 2024)</t>
         </is>
       </c>
-      <c r="K16" s="12" t="inlineStr">
+      <c r="K16" s="13" t="inlineStr">
         <is>
           <t>See also case studies on Melbourne Plus in the Chanc. Ed. SASS spreadsheet.</t>
         </is>
       </c>
-      <c r="L16" s="14" t="n"/>
-      <c r="M16" s="14" t="n"/>
-      <c r="N16" s="14" t="n"/>
-      <c r="O16" s="14" t="n"/>
-      <c r="P16" s="14" t="n"/>
-      <c r="Q16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="220" customHeight="1">
-      <c r="B17" s="10" t="inlineStr">
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+    </row>
+    <row r="17" ht="188" customHeight="1">
+      <c r="B17" s="11" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C17" s="11" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>Exceptional education</t>
         </is>
       </c>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Provide our students with learning experiences that help them build the knowledge, skills and relationships to lead change for sustainable societies.</t>
         </is>
       </c>
-      <c r="E17" s="11" t="inlineStr">
+      <c r="E17" s="12" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating how graduates contribute to sustainability through their careers or communities.</t>
         </is>
       </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>In end-2025 reporting your area reported on the related SP2030 target 3b(ii) (click the ref in Column H to see it in full in Tab 3). Please build on this rather than repeating it, focusing on what is new in 2026.
-Can you list any notable alumni working in sustainability? (Name, course and graduating year, a short summary and a link to a profile if available; please note whether consent to be featured is likely.)
+      <c r="F17" s="13" t="inlineStr">
+        <is>
+          <t>Can you list any notable alumni working in sustainability? (Name, course and graduating year, a short summary and a link to a profile if available; please note whether consent to be featured is likely.)
+In end-2025 reporting your area reported on the related SP2030 target 3b(ii) (click the ref in Column H to see it in full in Tab 3).
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
       </c>
-      <c r="G17" s="12" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>We will use nominated alumni to develop short graduate profiles for the 2026 Sustainability Report (subject to consent), and record any faculty approaches to tracking graduate outcomes to inform how this indicator is measured from 2027.</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>3b(ii)
 → view SR25 response</t>
         </is>
       </c>
-      <c r="I17" s="12" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="J17" s="12" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>A sustainability approach is taken at large scale student events, including MCCs, Exams &amp; Grads (no takeaway containers, reusable cutlery and plates (partnering with Green My Plate), water refill stations etc). The previously printed graduation ceremony program was converted to a digital offering in 2025. 
 The team are reviewing the process of testamur creation to reduce waste from templates becoming superseded when updates are made to signatories. 
@@ -941,17 +1106,17 @@
 We have met our 2025 target by shifting 100% of eligible on‑campus events to food vouchers instead of catering, reducing food waste while meeting required vendor minimums."</t>
         </is>
       </c>
-      <c r="K17" s="12" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>See details in Chancellery Ed. (SASS) spreadsheet, including data on sustainability-themed event participation in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="L17" s="14" t="n"/>
-      <c r="M17" s="14" t="n"/>
-      <c r="N17" s="14" t="n"/>
-      <c r="O17" s="14" t="n"/>
-      <c r="P17" s="14" t="n"/>
-      <c r="Q17" s="14" t="n"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
@@ -972,6 +1137,7 @@
     <hyperlink ref="H17" location="'3. SR25 responses'!B7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -981,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -994,104 +1160,148 @@
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Highlighted stories (optional)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3"/>
     <row r="4"/>
     <row r="5" ht="22" customHeight="1">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>How to use this spreadsheet</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
-        <is>
-          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Tuesday 15 December 2026 (early submission helps us develop case studies).</t>
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>Please share up to 3 stories from 2026 which highlight your faculty's/portfolio's sustainability progress and/or impact. These stories can directly relate to Sustainability 2030 targets and indicators, or sustainability more generally. Due: Thursday 24 December 2026 (Christmas shutdown) (early submission helps us develop case studies).</t>
         </is>
       </c>
     </row>
     <row r="6"/>
     <row r="7"/>
     <row r="8" ht="39" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="D8" s="18" t="inlineStr">
         <is>
           <t>Related Sustainability 2030 targets (optional)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>Images and other media</t>
         </is>
       </c>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="F8" s="18" t="inlineStr">
         <is>
           <t>Links and supporting documentation</t>
         </is>
       </c>
     </row>
     <row r="9" ht="90" customHeight="1">
-      <c r="B9" s="18" t="inlineStr"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>• Please include a brief description of a project or activity that has made a significant contribution to sustainability at the University (up to 250 words)
 • Summarise the benefits. Benefits may relate to operational outcomes, environmental/social outcomes, and sector benefits.</t>
         </is>
       </c>
-      <c r="D9" s="18" t="inlineStr"/>
-      <c r="E9" s="18" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr"/>
+      <c r="E9" s="19" t="inlineStr">
         <is>
           <t>(link to OneDrive/SharePoint files or published online content preferred)</t>
         </is>
       </c>
-      <c r="F9" s="18" t="inlineStr"/>
+      <c r="F9" s="19" t="inlineStr"/>
     </row>
     <row r="10" ht="120" customHeight="1">
       <c r="A10" t="n">
         <v>1</v>
       </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="120" customHeight="1">
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="120" customHeight="1">
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1099,6 +1309,7 @@
     <mergeCell ref="C5:F6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1108,7 +1319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:R10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1120,101 +1331,146 @@
     <col width="60" customWidth="1" min="7" max="7"/>
     <col width="34" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Your SR25 responses – Student and Scholarly Services (SaSS)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="17" t="inlineStr">
         <is>
           <t>Your responses to the end-2025 reporting request, against the former Sustainability Plan 2030 (SP2030) targets. For reference only – please do not edit. Use the 'Back to request' links to return to the reporting template.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1">
-      <c r="B4" s="19" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr">
         <is>
           <t>← Back to request</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Student and scholarly services</t>
         </is>
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>SR25 ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>SP2030 target</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>2025 reporting request</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Confirmed end-2025 status</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>OPTION 1: Target-level reporting</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>OPTION 2: Indicator-level reporting</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Supporting information/comments</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Related SR26 indicator(s)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="409" customHeight="1">
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>3b(ii)</t>
         </is>
       </c>
-      <c r="C7" s="12" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>The University community shows increased uptake of positive sustainability skills, knowledge and behaviours through non-formal and informal learning</t>
         </is>
       </c>
-      <c r="D7" s="12" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>Number of sustainability-focused events and participants in 2024</t>
         </is>
       </c>
-      <c r="E7" s="12" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F7" s="12" t="inlineStr">
+      <c r="F7" s="13" t="inlineStr">
         <is>
           <t>A sustainability approach is taken at large scale student events, including MCCs, Exams &amp; Grads (no takeaway containers, reusable cutlery and plates (partnering with Green My Plate), water refill stations etc). The previously printed graduation ceremony program was converted to a digital offering in 2025. 
 The team are reviewing the process of testamur creation to reduce waste from templates becoming superseded when updates are made to signatories. 
@@ -1243,122 +1499,122 @@
 We have met our 2025 target by shifting 100% of eligible on‑campus events to food vouchers instead of catering, reducing food waste while meeting required vendor minimums."</t>
         </is>
       </c>
-      <c r="G7" s="12" t="inlineStr"/>
-      <c r="H7" s="12" t="inlineStr">
+      <c r="G7" s="13" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr">
         <is>
           <t>See details in Chancellery Ed. (SASS) spreadsheet, including data on sustainability-themed event participation in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="I7" s="12" t="inlineStr">
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>3b(vii)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>The University community shows increased uptake of positive sustainability skills, knowledge and behaviours through non-formal and informal learning</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Number of participants in Melbourne Plus sustainability stream; case studies describing participant outcomes.</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr"/>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="F8" s="13" t="inlineStr"/>
+      <c r="G8" s="13" t="inlineStr">
         <is>
           <t>Number of student particpation in a sustainability activity in 2025: 466 (14% increase YTY from 2024).
 Number of total credentials released for Sustainability Advocacy in 2025: 297 (29% increase YTY from 2024)</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="13" t="inlineStr">
         <is>
           <t>See also case studies on Melbourne Plus in the Chanc. Ed. SASS spreadsheet.</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="13" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>3c</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>The University offers a suite of student-centered, formal and non-formal applied sustainability learning opportunities, informed by inter and trans-disciplinary approaches</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Number of participants in relevant applied learning, internship and volunteering opportunities</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F9" s="12" t="inlineStr"/>
-      <c r="G9" s="12" t="inlineStr">
+      <c r="F9" s="13" t="inlineStr"/>
+      <c r="G9" s="13" t="inlineStr">
         <is>
           <t>Number of new opportunities added to Melbourne Plus Catalogue where students can participate and earn a Sustainability Advocacy credential: 5 (bringing the total offering in the stream to 17)
 The range of these opportunities span from volunteering for campus student events contributing to sustainability, auditing campus accessibility features and infrastructures, to online learning modules.</t>
         </is>
       </c>
-      <c r="H9" s="12" t="inlineStr">
+      <c r="H9" s="13" t="inlineStr">
         <is>
           <t>See also additional data in Chanc. Ed. Spreadsheet regarding sustainability-themed events in UOM managed student accommodation</t>
         </is>
       </c>
-      <c r="I9" s="12" t="inlineStr"/>
+      <c r="I9" s="13" t="inlineStr"/>
     </row>
     <row r="10" ht="160" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>4a(iv)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Sustainability is integrated into curriculum to an extent that conscientiously extends, beyond a base threshold, each discipline’s (and associated professions/industries’) knowledge of the helpful and harmful impacts it has for the environmental and human systems we depend on.</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>List of subjects and courses with sustainability-related content</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>Met or exceeded</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>The 2026 Handbook provides an overview of sustainability-related Courses, Majors, Subjects - via the Search function. 
 This builds on the 2017-2020 Sustainabilty Plan which requires Faculties to incorporate sustainability knowledge and values into the Graduate Attributes of courses.</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr"/>
-      <c r="H10" s="12" t="inlineStr"/>
-      <c r="I10" s="12" t="inlineStr"/>
+      <c r="G10" s="13" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1368,6 +1624,7 @@
     <hyperlink ref="B4" location="'1. Reporting template'!A1"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1377,7 +1634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:R12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1395,321 +1652,360 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
     <col width="26" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2" ht="39" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="1" t="n"/>
+      <c r="B1" s="1" t="n"/>
+      <c r="C1" s="1" t="n"/>
+      <c r="D1" s="1" t="n"/>
+      <c r="E1" s="1" t="n"/>
+      <c r="F1" s="1" t="n"/>
+      <c r="G1" s="1" t="n"/>
+      <c r="H1" s="1" t="n"/>
+      <c r="I1" s="1" t="n"/>
+      <c r="J1" s="1" t="n"/>
+      <c r="K1" s="1" t="n"/>
+      <c r="L1" s="1" t="n"/>
+      <c r="M1" s="1" t="n"/>
+      <c r="N1" s="1" t="n"/>
+      <c r="O1" s="1" t="n"/>
+      <c r="P1" s="1" t="n"/>
+      <c r="Q1" s="1" t="n"/>
+      <c r="R1" s="1" t="n"/>
+    </row>
+    <row r="2" ht="58" customHeight="1">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Quantitative data – Student and Scholarly Services (SaSS)</t>
         </is>
       </c>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="n"/>
+      <c r="I2" s="1" t="n"/>
+      <c r="J2" s="1" t="n"/>
+      <c r="K2" s="1" t="n"/>
+      <c r="L2" s="1" t="n"/>
+      <c r="M2" s="1" t="n"/>
+      <c r="N2" s="1" t="n"/>
+      <c r="O2" s="1" t="n"/>
+      <c r="P2" s="1" t="n"/>
+      <c r="Q2" s="1" t="n"/>
+      <c r="R2" s="1" t="n"/>
     </row>
     <row r="3" ht="48" customHeight="1">
-      <c r="B3" s="16" t="inlineStr">
-        <is>
-          <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Tuesday 15 December 2026.</t>
+      <c r="B3" s="17" t="inlineStr">
+        <is>
+          <t>These figures feed the Sustainability Databook (the University's authoritative quantitative source). Previous years are shown for context – please do not alter. Please provide the CY2026 value (provisional or year-to-date figures are fine; we will confirm final figures with you in January–February), the data source, and any change to definition or boundary. Due: Thursday 24 December 2026 (Christmas shutdown).</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5" ht="27" customHeight="1">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>Context only (please do not alter)</t>
         </is>
       </c>
-      <c r="K5" s="6" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Please fill in these cells</t>
         </is>
       </c>
     </row>
     <row r="6" ht="60" customHeight="1">
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="8" t="inlineStr">
         <is>
           <t>Indicator</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="D6" s="8" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="8" t="inlineStr">
         <is>
           <t>Baseline</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>CY2023</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>CY2024</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>CY2025</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>Data status</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="9" t="inlineStr">
         <is>
           <t>CY2026 value</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>Data source (file name, link or system)</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="M6" s="9" t="inlineStr">
         <is>
           <t>Change to definition or boundary?</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="N6" s="9" t="inlineStr">
         <is>
           <t>Notes / limitations</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="9" t="inlineStr">
         <is>
           <t>Useful case studies</t>
         </is>
       </c>
     </row>
     <row r="7" ht="46" customHeight="1">
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>No instructions – context only.</t>
         </is>
       </c>
-      <c r="C7" s="21" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr"/>
-      <c r="E7" s="21" t="inlineStr"/>
-      <c r="F7" s="21" t="inlineStr"/>
-      <c r="G7" s="21" t="inlineStr"/>
-      <c r="H7" s="21" t="inlineStr"/>
-      <c r="I7" s="21" t="inlineStr"/>
-      <c r="J7" s="21" t="inlineStr"/>
-      <c r="K7" s="21" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr"/>
+      <c r="D7" s="22" t="inlineStr"/>
+      <c r="E7" s="22" t="inlineStr"/>
+      <c r="F7" s="22" t="inlineStr"/>
+      <c r="G7" s="22" t="inlineStr"/>
+      <c r="H7" s="22" t="inlineStr"/>
+      <c r="I7" s="22" t="inlineStr"/>
+      <c r="J7" s="22" t="inlineStr"/>
+      <c r="K7" s="22" t="inlineStr">
         <is>
           <t>Please enter numerical values</t>
         </is>
       </c>
-      <c r="L7" s="21" t="inlineStr">
+      <c r="L7" s="22" t="inlineStr">
         <is>
           <t>Please provide a file name or link to the data source</t>
         </is>
       </c>
-      <c r="M7" s="21" t="inlineStr">
+      <c r="M7" s="22" t="inlineStr">
         <is>
           <t>Describe any change since last year (or 'No change')</t>
         </is>
       </c>
-      <c r="N7" s="21" t="inlineStr">
+      <c r="N7" s="22" t="inlineStr">
         <is>
           <t>Please add any additional notes here</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>Please provide information on any useful case studies</t>
         </is>
       </c>
     </row>
     <row r="8" ht="56" customHeight="1">
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Evidence of sustainability focused experiential and cocurricular learning</t>
         </is>
       </c>
-      <c r="D8" s="12" t="inlineStr">
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>Number of Co-curricular Learning</t>
         </is>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F8" s="22" t="n"/>
-      <c r="G8" s="22" t="n">
+      <c r="F8" s="23" t="n"/>
+      <c r="G8" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="J8" s="12" t="inlineStr">
+      <c r="J8" s="13" t="inlineStr">
         <is>
           <t>Data held</t>
         </is>
       </c>
-      <c r="K8" s="14" t="n"/>
-      <c r="L8" s="14" t="n"/>
-      <c r="M8" s="14" t="n"/>
-      <c r="N8" s="14" t="n"/>
-      <c r="O8" s="14" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
     </row>
     <row r="9" ht="39" customHeight="1">
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C9" s="12" t="inlineStr"/>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr"/>
+      <c r="D9" s="13" t="inlineStr">
         <is>
           <t>Number of Experiential Learning Projects</t>
         </is>
       </c>
-      <c r="E9" s="12" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="22" t="n"/>
-      <c r="I9" s="22" t="n"/>
-      <c r="J9" s="12" t="inlineStr">
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="23" t="n"/>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="23" t="n"/>
+      <c r="J9" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="K9" s="13" t="n"/>
+      <c r="L9" s="13" t="n"/>
+      <c r="M9" s="13" t="n"/>
+      <c r="N9" s="13" t="n"/>
+      <c r="O9" s="13" t="n"/>
     </row>
     <row r="10" ht="39" customHeight="1">
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>EE1(c)</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr"/>
-      <c r="D10" s="12" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr"/>
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Number of Participating Students</t>
         </is>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="22" t="n"/>
-      <c r="H10" s="22" t="n"/>
-      <c r="I10" s="22" t="n"/>
-      <c r="J10" s="12" t="inlineStr">
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="23" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="23" t="n"/>
+      <c r="J10" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K10" s="12" t="n"/>
-      <c r="L10" s="12" t="n"/>
-      <c r="M10" s="12" t="n"/>
-      <c r="N10" s="12" t="n"/>
-      <c r="O10" s="12" t="n"/>
+      <c r="K10" s="13" t="n"/>
+      <c r="L10" s="13" t="n"/>
+      <c r="M10" s="13" t="n"/>
+      <c r="N10" s="13" t="n"/>
+      <c r="O10" s="13" t="n"/>
     </row>
     <row r="11" ht="72" customHeight="1">
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C11" s="12" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating how graduates contribute to sustainability through their careers or communities</t>
         </is>
       </c>
-      <c r="D11" s="12" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Alumni that contribute to sustainability</t>
         </is>
       </c>
-      <c r="E11" s="12" t="inlineStr">
+      <c r="E11" s="13" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="22" t="n"/>
-      <c r="H11" s="22" t="n"/>
-      <c r="I11" s="22" t="n"/>
-      <c r="J11" s="12" t="inlineStr">
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="23" t="n"/>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="23" t="n"/>
+      <c r="J11" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K11" s="14" t="n"/>
-      <c r="L11" s="14" t="n"/>
-      <c r="M11" s="14" t="n"/>
-      <c r="N11" s="14" t="n"/>
-      <c r="O11" s="14" t="n"/>
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
+      <c r="N11" s="15" t="n"/>
+      <c r="O11" s="15" t="n"/>
     </row>
     <row r="12" ht="39" customHeight="1">
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
         <is>
           <t>EE1(d)</t>
         </is>
       </c>
-      <c r="C12" s="12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="C12" s="13" t="inlineStr"/>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>Alumni profiles demonstrating sustainability contribution</t>
         </is>
       </c>
-      <c r="E12" s="12" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="22" t="n"/>
-      <c r="H12" s="22" t="n"/>
-      <c r="I12" s="22" t="n"/>
-      <c r="J12" s="12" t="inlineStr">
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="23" t="n"/>
+      <c r="H12" s="23" t="n"/>
+      <c r="I12" s="23" t="n"/>
+      <c r="J12" s="13" t="inlineStr">
         <is>
           <t>New – no data yet</t>
         </is>
       </c>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
+      <c r="K12" s="13" t="n"/>
+      <c r="L12" s="13" t="n"/>
+      <c r="M12" s="13" t="n"/>
+      <c r="N12" s="13" t="n"/>
+      <c r="O12" s="13" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
@@ -1724,6 +2020,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
+++ b/output/central_unit_requests/SaSS - SR26 sustainability reporting request.xlsx
@@ -747,9 +747,9 @@
     <col width="48" customWidth="1" min="12" max="12"/>
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="30" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
+    <col width="36" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
     <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
@@ -808,7 +808,8 @@
         <is>
           <t>• For each row below, describe progress towards the target (Column L) and/or respond to the 2026 reporting request (Column M)
 • Provide supporting information if required (Column N), including links to documents or images
-• Note the source of your information and any limitations (Column O), then confirm the information is accurate (Columns P–Q)
+• Note the source of your information, any limitations and the person closest to the data (Column O)
+• Please return the spreadsheet once it has been reviewed and confirmed by your area's senior lead
 • Where a related end-2025 target existed, click the ref in Column H to see your full SR25 response (Tab 3)
 • Use Tab 2 of this spreadsheet to highlight key sustainability stories (optional)
 • 2026 is a transition year: Sustainability 2030 launched ~20 October 2026, so report on activity across all of 2026 and any early actions since launch. No target status rating is requested this year.
@@ -847,7 +848,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="60" customHeight="1">
+    <row r="14" ht="42" customHeight="1">
       <c r="B14" s="8" t="inlineStr">
         <is>
           <t>Ref</t>
@@ -915,17 +916,7 @@
       </c>
       <c r="O14" s="9" t="inlineStr">
         <is>
-          <t>Data source and limitations</t>
-        </is>
-      </c>
-      <c r="P14" s="9" t="inlineStr">
-        <is>
-          <t>Data owner confirms information is accurate</t>
-        </is>
-      </c>
-      <c r="Q14" s="9" t="inlineStr">
-        <is>
-          <t>Confirmed by (name, role, date)</t>
+          <t>Data source, limitations and contact person</t>
         </is>
       </c>
     </row>
@@ -957,17 +948,7 @@
       </c>
       <c r="O15" s="10" t="inlineStr">
         <is>
-          <t>Where did this information come from (system, report, survey, person)? Note any gaps or limitations.</t>
-        </is>
-      </c>
-      <c r="P15" s="10" t="inlineStr">
-        <is>
-          <t>Select 'Yes' to confirm the information provided is accurate and can be used for reporting</t>
-        </is>
-      </c>
-      <c r="Q15" s="10" t="inlineStr">
-        <is>
-          <t>Name, role and date of the person confirming</t>
+          <t>Where did this information come from (system, report, survey)? Note any gaps or limitations, and the person closest to the data we can follow up with.</t>
         </is>
       </c>
     </row>
@@ -994,7 +975,7 @@
       </c>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your Faculty/Portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.
+          <t>Please provide examples of sustainability-focused experiential or co-curricular learning offered or supported by your portfolio (e.g. Wattle Fellowship, Melbourne Plus or similar), could include participation where available and a brief description of the learning experience and outcomes.
 In end-2025 reporting your area reported on the related SP2030 target 3b(vii) (click the ref in Column H to see it in full in Tab 3).
 Quantitative figures for this indicator are requested separately in Tab 4 (Quantitative data).</t>
         </is>
@@ -1030,8 +1011,6 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="15" t="n"/>
       <c r="O16" s="15" t="n"/>
-      <c r="P16" s="15" t="n"/>
-      <c r="Q16" s="15" t="n"/>
     </row>
     <row r="17" ht="188" customHeight="1">
       <c r="B17" s="11" t="inlineStr">
@@ -1115,23 +1094,16 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="15" t="n"/>
       <c r="O17" s="15" t="n"/>
-      <c r="P17" s="15" t="n"/>
-      <c r="Q17" s="15" t="n"/>
     </row>
     <row r="18"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="4">
     <mergeCell ref="C13:G13"/>
-    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="L13:O13"/>
     <mergeCell ref="D4:G8"/>
     <mergeCell ref="B4:C8"/>
   </mergeCells>
-  <dataValidations count="1">
-    <dataValidation sqref="P16:P17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid entry" error="Please select from the dropdown" type="list">
-      <formula1>=Lists!$C$2:$C$4</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink ref="H16" location="'3. SR25 responses'!B8"/>
     <hyperlink ref="H17" location="'3. SR25 responses'!B7"/>
